--- a/Bredinin.AlloyEditor.WebApi/Resources/Dictionaries/ChemicalElements.xlsx
+++ b/Bredinin.AlloyEditor.WebApi/Resources/Dictionaries/ChemicalElements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bredi\Desktop\project\Bredinin.AlloyEditor\Bredinin.AlloyEditor.WebApi\Resources\Dictionaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26AD2C4D-5A51-4482-99DE-AA025B69F2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15E1108-1014-47E4-B1D0-9C885FA4553F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="5310" windowWidth="28800" windowHeight="15345" xr2:uid="{C63E09A9-B350-4241-B722-26B955AF2026}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C63E09A9-B350-4241-B722-26B955AF2026}"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20250603_fef23f" sheetId="2" r:id="rId1"/>
@@ -27,12 +27,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -48,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="242">
   <si>
     <t>Symbol</t>
   </si>
@@ -761,9 +756,6 @@
     <t>72.64</t>
   </si>
   <si>
-    <t>5.32</t>
-  </si>
-  <si>
     <t>As</t>
   </si>
   <si>
@@ -776,14 +768,14 @@
     <t>74.9216</t>
   </si>
   <si>
-    <t/>
+    <t>12.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -813,9 +805,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1203,21 +1196,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A04BD21D-574F-4A46-9F3F-E531A302F3E1}">
   <dimension ref="A1:I51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1239,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1275,7 +1268,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1304,7 +1297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -1333,7 +1326,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -1362,7 +1355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1391,7 +1384,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1420,7 +1413,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>39</v>
       </c>
@@ -1449,7 +1442,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>44</v>
       </c>
@@ -1478,7 +1471,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>49</v>
       </c>
@@ -1507,7 +1500,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>54</v>
       </c>
@@ -1536,7 +1529,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -1565,7 +1558,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
@@ -1594,7 +1587,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>69</v>
       </c>
@@ -1623,7 +1616,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>74</v>
       </c>
@@ -1652,7 +1645,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>79</v>
       </c>
@@ -1681,7 +1674,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
         <v>84</v>
       </c>
@@ -1710,7 +1703,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
         <v>89</v>
       </c>
@@ -1739,7 +1732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>93</v>
       </c>
@@ -1768,7 +1761,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>98</v>
       </c>
@@ -1797,7 +1790,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>102</v>
       </c>
@@ -1826,7 +1819,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
         <v>106</v>
       </c>
@@ -1855,7 +1848,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
         <v>110</v>
       </c>
@@ -1884,7 +1877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
         <v>114</v>
       </c>
@@ -1913,7 +1906,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
         <v>119</v>
       </c>
@@ -1942,7 +1935,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
         <v>124</v>
       </c>
@@ -1971,7 +1964,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
         <v>128</v>
       </c>
@@ -2000,7 +1993,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
         <v>132</v>
       </c>
@@ -2029,7 +2022,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
         <v>137</v>
       </c>
@@ -2058,7 +2051,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
         <v>141</v>
       </c>
@@ -2087,7 +2080,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
         <v>146</v>
       </c>
@@ -2116,7 +2109,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
         <v>151</v>
       </c>
@@ -2145,7 +2138,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
         <v>156</v>
       </c>
@@ -2174,7 +2167,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
         <v>161</v>
       </c>
@@ -2203,7 +2196,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
         <v>166</v>
       </c>
@@ -2232,7 +2225,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
         <v>171</v>
       </c>
@@ -2261,7 +2254,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
         <v>176</v>
       </c>
@@ -2290,7 +2283,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
         <v>181</v>
       </c>
@@ -2319,7 +2312,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
         <v>186</v>
       </c>
@@ -2348,7 +2341,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
         <v>191</v>
       </c>
@@ -2377,7 +2370,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
         <v>195</v>
       </c>
@@ -2406,7 +2399,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
         <v>200</v>
       </c>
@@ -2435,7 +2428,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="1" t="s">
         <v>204</v>
       </c>
@@ -2464,7 +2457,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="1" t="s">
         <v>208</v>
       </c>
@@ -2493,7 +2486,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="1" t="s">
         <v>213</v>
       </c>
@@ -2522,7 +2515,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="1" t="s">
         <v>217</v>
       </c>
@@ -2551,7 +2544,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="1" t="s">
         <v>221</v>
       </c>
@@ -2580,7 +2573,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="1" t="s">
         <v>225</v>
       </c>
@@ -2609,7 +2602,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="1" t="s">
         <v>229</v>
       </c>
@@ -2638,7 +2631,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="1" t="s">
         <v>233</v>
       </c>
@@ -2663,28 +2656,28 @@
       <c r="H50">
         <v>4</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="1" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="C51" t="b">
+        <v>0</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>239</v>
-      </c>
-      <c r="C51" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="E51">
         <v>33</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G51">
         <v>15</v>
@@ -2692,14 +2685,15 @@
       <c r="H51">
         <v>4</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>242</v>
+      <c r="I51" s="2" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2707,7 +2701,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D5336E-ADBA-4EF2-A712-3FC088F61715}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
